--- a/Configs/GameConfig/Datas/PFTag.xlsx
+++ b/Configs/GameConfig/Datas/PFTag.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="PFTag" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>##var</t>
   </si>
@@ -129,6 +129,15 @@
   </si>
   <si>
     <t>生命根标签</t>
+  </si>
+  <si>
+    <t>MP</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Life.MP</t>
   </si>
   <si>
     <t>HP</t>
@@ -154,19 +163,16 @@
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
-      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Carlito"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -174,7 +180,6 @@
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -182,14 +187,12 @@
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="Calibri"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -197,7 +200,6 @@
       <sz val="18"/>
       <color theme="3"/>
       <name val="Calibri"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -205,7 +207,6 @@
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="Calibri"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -213,7 +214,6 @@
       <sz val="15"/>
       <color theme="3"/>
       <name val="Calibri"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -221,7 +221,6 @@
       <sz val="13"/>
       <color theme="3"/>
       <name val="Calibri"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -229,14 +228,12 @@
       <sz val="11"/>
       <color theme="3"/>
       <name val="Calibri"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -244,7 +241,6 @@
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="Calibri"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -252,7 +248,6 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -260,14 +255,12 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -275,42 +268,36 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="Calibri"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="Calibri"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -622,210 +609,357 @@
     </border>
   </borders>
   <cellStyleXfs count="50">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+  <cellXfs count="51">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="4" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="3" applyFill="1" borderId="1" applyBorder="1" xfId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="5" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="6" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="7" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="12">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="8" applyFont="1" fillId="0" applyFill="1" borderId="2" applyBorder="1" xfId="13">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="9" applyFont="1" fillId="0" applyFill="1" borderId="2" applyBorder="1" xfId="14">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="10" applyFont="1" fillId="0" applyFill="1" borderId="3" applyBorder="1" xfId="15">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="10" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="16">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="11" applyFont="1" fillId="4" applyFill="1" borderId="4" applyBorder="1" xfId="17">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="12" applyFont="1" fillId="5" applyFill="1" borderId="5" applyBorder="1" xfId="18">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="13" applyFont="1" fillId="5" applyFill="1" borderId="4" applyBorder="1" xfId="19">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="14" applyFont="1" fillId="6" applyFill="1" borderId="6" applyBorder="1" xfId="20">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="15" applyFont="1" fillId="0" applyFill="1" borderId="7" applyBorder="1" xfId="21">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="16" applyFont="1" fillId="0" applyFill="1" borderId="8" applyBorder="1" xfId="22">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="17" applyFont="1" fillId="7" applyFill="1" borderId="0" applyBorder="1" xfId="23">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="8" applyFill="1" borderId="0" applyBorder="1" xfId="24">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="9" applyFill="1" borderId="0" applyBorder="1" xfId="25">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="20" applyFont="1" fillId="10" applyFill="1" borderId="0" applyBorder="1" xfId="26">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="21" applyFont="1" fillId="11" applyFill="1" borderId="0" applyBorder="1" xfId="27">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="21" applyFont="1" fillId="12" applyFill="1" borderId="0" applyBorder="1" xfId="28">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="20" applyFont="1" fillId="13" applyFill="1" borderId="0" applyBorder="1" xfId="29">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="20" applyFont="1" fillId="14" applyFill="1" borderId="0" applyBorder="1" xfId="30">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="21" applyFont="1" fillId="15" applyFill="1" borderId="0" applyBorder="1" xfId="31">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="21" applyFont="1" fillId="16" applyFill="1" borderId="0" applyBorder="1" xfId="32">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="20" applyFont="1" fillId="17" applyFill="1" borderId="0" applyBorder="1" xfId="33">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="20" applyFont="1" fillId="18" applyFill="1" borderId="0" applyBorder="1" xfId="34">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="21" applyFont="1" fillId="19" applyFill="1" borderId="0" applyBorder="1" xfId="35">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="21" applyFont="1" fillId="20" applyFill="1" borderId="0" applyBorder="1" xfId="36">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="20" applyFont="1" fillId="21" applyFill="1" borderId="0" applyBorder="1" xfId="37">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="20" applyFont="1" fillId="22" applyFill="1" borderId="0" applyBorder="1" xfId="38">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="21" applyFont="1" fillId="23" applyFill="1" borderId="0" applyBorder="1" xfId="39">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="21" applyFont="1" fillId="24" applyFill="1" borderId="0" applyBorder="1" xfId="40">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="20" applyFont="1" fillId="25" applyFill="1" borderId="0" applyBorder="1" xfId="41">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="20" applyFont="1" fillId="26" applyFill="1" borderId="0" applyBorder="1" xfId="42">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="21" applyFont="1" fillId="27" applyFill="1" borderId="0" applyBorder="1" xfId="43">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="21" applyFont="1" fillId="28" applyFill="1" borderId="0" applyBorder="1" xfId="44">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="20" applyFont="1" fillId="29" applyFill="1" borderId="0" applyBorder="1" xfId="45">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="20" applyFont="1" fillId="30" applyFill="1" borderId="0" applyBorder="1" xfId="46">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="21" applyFont="1" fillId="31" applyFill="1" borderId="0" applyBorder="1" xfId="47">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="21" applyFont="1" fillId="32" applyFill="1" borderId="0" applyBorder="1" xfId="48">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="20" applyFont="1" fillId="33" applyFill="1" borderId="0" applyBorder="1" xfId="49">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
   </cellXfs>
   <cellStyles count="50">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="Normal" xfId="49"/>
+    <cellStyle name="常规" xfId="1" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="2" builtinId="3"/>
+    <cellStyle name="货币" xfId="3" builtinId="4"/>
+    <cellStyle name="百分比" xfId="4" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="6" builtinId="7"/>
+    <cellStyle name="超链接" xfId="7" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="8" builtinId="9"/>
+    <cellStyle name="注释" xfId="9" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="10" builtinId="11"/>
+    <cellStyle name="标题" xfId="11" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="12" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="13" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="14" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="15" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="16" builtinId="19"/>
+    <cellStyle name="输入" xfId="17" builtinId="20"/>
+    <cellStyle name="输出" xfId="18" builtinId="21"/>
+    <cellStyle name="计算" xfId="19" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="20" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="21" builtinId="24"/>
+    <cellStyle name="汇总" xfId="22" builtinId="25"/>
+    <cellStyle name="好" xfId="23" builtinId="26"/>
+    <cellStyle name="差" xfId="24" builtinId="27"/>
+    <cellStyle name="适中" xfId="25" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="26" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="27" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="28" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="29" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="30" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="31" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="32" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="33" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="34" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="35" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="36" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="37" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="38" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="39" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="40" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="41" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="42" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="43" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="47" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="48" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="49" builtinId="52"/>
+    <cellStyle name="Normal" xfId="0"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
@@ -1245,7 +1379,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
   <cols>
     <col min="2" max="4" width="15" customWidth="1"/>
@@ -1253,208 +1387,225 @@
     <col min="6" max="6" width="19.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" spans="1:6">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="15">
+      <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="50" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="15" spans="1:6">
-      <c r="A2" s="1" t="s">
+    <row r="2" ht="15">
+      <c r="A2" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="50" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" ht="15" spans="1:6">
-      <c r="A3" s="1" t="s">
+    <row r="3" ht="15">
+      <c r="A3" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="50" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" ht="15" spans="1:6">
-      <c r="A4" s="1" t="s">
+    <row r="4" ht="15">
+      <c r="A4" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="50" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="50" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="B5">
+    <row r="5">
+      <c r="B5" s="0">
         <v>0</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="0">
         <v>-1</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="0" t="s">
         <v>15</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="0" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
-      <c r="B6">
+    <row r="6">
+      <c r="B6" s="0">
         <v>1</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="0">
         <v>0</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="0" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
-      <c r="B7">
+    <row r="7">
+      <c r="B7" s="0">
         <v>2</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="0">
         <v>0</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="0" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
-      <c r="B8">
+    <row r="8">
+      <c r="B8" s="0">
         <v>5</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="0">
         <v>2</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="0" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
-      <c r="B9">
+    <row r="9">
+      <c r="B9" s="0">
         <v>6</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="0">
         <v>2</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="0" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
-      <c r="B10">
+    <row r="10">
+      <c r="B10" s="0">
         <v>7</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="0">
         <v>2</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="0" t="s">
         <v>29</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="0" t="s">
         <v>30</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" s="0" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
-      <c r="B11">
+    <row r="11">
+      <c r="B11" s="0">
         <v>3</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="0">
         <v>-1</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="0" t="s">
         <v>32</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="0" t="s">
         <v>33</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="0" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
-      <c r="B12">
+    <row r="12">
+      <c r="B12" s="0">
+        <v>8</v>
+      </c>
+      <c r="C12" s="0">
+        <v>3</v>
+      </c>
+      <c r="D12" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="E12" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="F12" s="0" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="0">
         <v>4</v>
       </c>
-      <c r="C12">
+      <c r="C13" s="0">
         <v>3</v>
       </c>
-      <c r="D12" t="s">
-        <v>34</v>
-      </c>
-      <c r="E12" t="s">
-        <v>35</v>
-      </c>
-      <c r="F12" t="s">
-        <v>36</v>
+      <c r="D13" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13" s="0" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
